--- a/dataset_benchmark/AUDIO_299.xlsx
+++ b/dataset_benchmark/AUDIO_299.xlsx
@@ -1,12 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\merged_partition_content\Khoi_Project\FPT-Assistant-v3\dataset_benchmark\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="15420" windowHeight="8364"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -883,32 +891,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -934,48 +943,171 @@
         <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -983,7 +1115,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1173,20 +1305,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:T1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="178.13"/>
+    <col min="1" max="1" width="178.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1345,7 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1232,7 +1367,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1256,7 +1391,7 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
         <v>1</v>
@@ -1278,31 +1413,31 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:20" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1326,7 +1461,7 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1350,7 +1485,7 @@
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1374,7 +1509,7 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -1398,7 +1533,7 @@
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1422,31 +1557,31 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1470,31 +1605,31 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -1518,7 +1653,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -1542,7 +1677,7 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -1566,31 +1701,31 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -1614,7 +1749,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -1638,7 +1773,7 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -1662,7 +1797,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -1686,7 +1821,7 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -1710,7 +1845,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
@@ -1734,7 +1869,7 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -1758,31 +1893,31 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-    </row>
-    <row r="26">
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
@@ -1806,7 +1941,7 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
@@ -1830,7 +1965,7 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
@@ -1854,7 +1989,7 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>27</v>
       </c>
@@ -1878,7 +2013,7 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
@@ -1902,7 +2037,7 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
@@ -1926,7 +2061,7 @@
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>30</v>
       </c>
@@ -1950,7 +2085,7 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
@@ -1974,7 +2109,7 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>32</v>
       </c>
@@ -1998,7 +2133,7 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>33</v>
       </c>
@@ -2022,7 +2157,7 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>34</v>
       </c>
@@ -2046,31 +2181,31 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-    </row>
-    <row r="38">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>36</v>
       </c>
@@ -2094,7 +2229,7 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>37</v>
       </c>
@@ -2118,7 +2253,7 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>38</v>
       </c>
@@ -2142,7 +2277,7 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
@@ -2166,7 +2301,7 @@
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>40</v>
       </c>
@@ -2190,7 +2325,7 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>41</v>
       </c>
@@ -2214,7 +2349,7 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>42</v>
       </c>
@@ -2238,7 +2373,7 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>43</v>
       </c>
@@ -2262,7 +2397,7 @@
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>44</v>
       </c>
@@ -2286,31 +2421,31 @@
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-    </row>
-    <row r="48">
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>46</v>
       </c>
@@ -2334,7 +2469,7 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>47</v>
       </c>
@@ -2358,7 +2493,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>48</v>
       </c>
@@ -2382,7 +2517,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>49</v>
       </c>
@@ -2406,7 +2541,7 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>50</v>
       </c>
@@ -2430,7 +2565,7 @@
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>51</v>
       </c>
@@ -2454,7 +2589,7 @@
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>52</v>
       </c>
@@ -2478,7 +2613,7 @@
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>53</v>
       </c>
@@ -2502,7 +2637,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>54</v>
       </c>
@@ -2526,7 +2661,7 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>55</v>
       </c>
@@ -2550,7 +2685,7 @@
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>56</v>
       </c>
@@ -2574,7 +2709,7 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>57</v>
       </c>
@@ -2598,7 +2733,7 @@
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>58</v>
       </c>
@@ -2622,7 +2757,7 @@
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>59</v>
       </c>
@@ -2646,31 +2781,31 @@
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="s">
+    <row r="62" spans="1:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-    </row>
-    <row r="63">
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="18"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>61</v>
       </c>
@@ -2694,31 +2829,31 @@
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="s">
+    <row r="64" spans="1:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-    </row>
-    <row r="65">
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="18"/>
+      <c r="R64" s="18"/>
+      <c r="S64" s="18"/>
+      <c r="T64" s="18"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>63</v>
       </c>
@@ -2742,7 +2877,7 @@
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>64</v>
       </c>
@@ -2766,7 +2901,7 @@
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>65</v>
       </c>
@@ -2790,55 +2925,55 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="s">
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
+      <c r="N68" s="24"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="24"/>
+      <c r="R68" s="24"/>
+      <c r="S68" s="24"/>
+      <c r="T68" s="24"/>
+    </row>
+    <row r="69" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-    </row>
-    <row r="70">
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="24"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="24"/>
+      <c r="R69" s="24"/>
+      <c r="S69" s="24"/>
+      <c r="T69" s="24"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>68</v>
       </c>
@@ -2862,8 +2997,8 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="s">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -2886,7 +3021,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>70</v>
       </c>
@@ -2910,7 +3045,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>71</v>
       </c>
@@ -2934,7 +3069,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>72</v>
       </c>
@@ -2958,7 +3093,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>73</v>
       </c>
@@ -2982,7 +3117,7 @@
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>74</v>
       </c>
@@ -3006,7 +3141,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>75</v>
       </c>
@@ -3030,7 +3165,7 @@
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>76</v>
       </c>
@@ -3054,7 +3189,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -3072,7 +3207,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>78</v>
       </c>
@@ -3090,7 +3225,7 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>79</v>
       </c>
@@ -3108,7 +3243,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>80</v>
       </c>
@@ -3126,7 +3261,7 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>81</v>
       </c>
@@ -3144,7 +3279,7 @@
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>82</v>
       </c>
@@ -3162,7 +3297,7 @@
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>83</v>
       </c>
@@ -3180,7 +3315,7 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>84</v>
       </c>
@@ -3198,25 +3333,25 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="s">
+    <row r="87" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
-    </row>
-    <row r="88">
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="21"/>
+      <c r="S87" s="21"/>
+      <c r="T87" s="21"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>86</v>
       </c>
@@ -3234,7 +3369,7 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>87</v>
       </c>
@@ -3252,7 +3387,7 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>88</v>
       </c>
@@ -3270,7 +3405,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>89</v>
       </c>
@@ -3288,7 +3423,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>90</v>
       </c>
@@ -3306,7 +3441,7 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>91</v>
       </c>
@@ -3324,7 +3459,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>92</v>
       </c>
@@ -3342,7 +3477,7 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>93</v>
       </c>
@@ -3360,7 +3495,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>94</v>
       </c>
@@ -3378,7 +3513,7 @@
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>95</v>
       </c>
@@ -3396,7 +3531,7 @@
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>96</v>
       </c>
@@ -3414,7 +3549,7 @@
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>97</v>
       </c>
@@ -3432,7 +3567,7 @@
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>98</v>
       </c>
@@ -3450,7 +3585,7 @@
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>99</v>
       </c>
@@ -3468,7 +3603,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>101</v>
       </c>
@@ -3486,7 +3621,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>102</v>
       </c>
@@ -3504,7 +3639,7 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>103</v>
       </c>
@@ -3522,7 +3657,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>104</v>
       </c>
@@ -3540,7 +3675,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>105</v>
       </c>
@@ -3558,7 +3693,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>106</v>
       </c>
@@ -3576,7 +3711,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>107</v>
       </c>
@@ -3594,7 +3729,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>108</v>
       </c>
@@ -3612,7 +3747,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>109</v>
       </c>
@@ -3630,7 +3765,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>110</v>
       </c>
@@ -3648,7 +3783,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>111</v>
       </c>
@@ -3666,7 +3801,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>112</v>
       </c>
@@ -3684,7 +3819,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>113</v>
       </c>
@@ -3702,7 +3837,7 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>114</v>
       </c>
@@ -3720,7 +3855,7 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>115</v>
       </c>
@@ -3738,7 +3873,7 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>116</v>
       </c>
@@ -3756,7 +3891,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>117</v>
       </c>
@@ -3774,7 +3909,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>118</v>
       </c>
@@ -3792,7 +3927,7 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>119</v>
       </c>
@@ -3810,7 +3945,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>120</v>
       </c>
@@ -3828,7 +3963,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>121</v>
       </c>
@@ -3846,7 +3981,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>122</v>
       </c>
@@ -3864,7 +3999,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>123</v>
       </c>
@@ -3882,7 +4017,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>124</v>
       </c>
@@ -3900,7 +4035,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>125</v>
       </c>
@@ -3918,7 +4053,7 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>126</v>
       </c>
@@ -3936,7 +4071,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>127</v>
       </c>
@@ -3954,7 +4089,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>128</v>
       </c>
@@ -3972,7 +4107,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>129</v>
       </c>
@@ -3990,7 +4125,7 @@
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>130</v>
       </c>
@@ -4008,7 +4143,7 @@
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>131</v>
       </c>
@@ -4026,7 +4161,7 @@
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>132</v>
       </c>
@@ -4044,7 +4179,7 @@
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>133</v>
       </c>
@@ -4062,7 +4197,7 @@
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>134</v>
       </c>
@@ -4080,7 +4215,7 @@
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>135</v>
       </c>
@@ -4098,7 +4233,7 @@
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>136</v>
       </c>
@@ -4116,7 +4251,7 @@
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>137</v>
       </c>
@@ -4134,7 +4269,7 @@
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>138</v>
       </c>
@@ -4152,7 +4287,7 @@
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>65</v>
       </c>
@@ -4170,7 +4305,7 @@
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>68</v>
       </c>
@@ -4188,7 +4323,7 @@
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>139</v>
       </c>
@@ -4206,7 +4341,7 @@
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>67</v>
       </c>
@@ -4224,7 +4359,7 @@
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>140</v>
       </c>
@@ -4242,7 +4377,7 @@
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>141</v>
       </c>
@@ -4260,7 +4395,7 @@
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>142</v>
       </c>
@@ -4278,7 +4413,7 @@
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>143</v>
       </c>
@@ -4296,7 +4431,7 @@
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>144</v>
       </c>
@@ -4314,7 +4449,7 @@
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>145</v>
       </c>
@@ -4332,7 +4467,7 @@
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>71</v>
       </c>
@@ -4350,7 +4485,7 @@
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>146</v>
       </c>
@@ -4375,7 +4510,7 @@
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>147</v>
       </c>
@@ -4400,7 +4535,7 @@
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>148</v>
       </c>
@@ -4425,7 +4560,7 @@
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>149</v>
       </c>
@@ -4450,7 +4585,7 @@
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>150</v>
       </c>
@@ -4475,7 +4610,7 @@
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>151</v>
       </c>
@@ -4500,7 +4635,7 @@
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>152</v>
       </c>
@@ -4525,7 +4660,7 @@
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>153</v>
       </c>
@@ -4550,7 +4685,7 @@
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>154</v>
       </c>
@@ -4575,7 +4710,7 @@
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>155</v>
       </c>
@@ -4600,7 +4735,7 @@
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>156</v>
       </c>
@@ -4625,7 +4760,7 @@
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>157</v>
       </c>
@@ -4650,7 +4785,7 @@
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
         <v>158</v>
       </c>
@@ -4675,7 +4810,7 @@
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
         <v>159</v>
       </c>
@@ -4700,7 +4835,7 @@
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>160</v>
       </c>
@@ -4725,7 +4860,7 @@
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>161</v>
       </c>
@@ -4750,7 +4885,7 @@
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>163</v>
       </c>
@@ -4775,7 +4910,7 @@
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>164</v>
       </c>
@@ -4800,7 +4935,7 @@
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>165</v>
       </c>
@@ -4825,7 +4960,7 @@
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>166</v>
       </c>
@@ -4850,7 +4985,7 @@
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>167</v>
       </c>
@@ -4875,7 +5010,7 @@
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>168</v>
       </c>
@@ -4900,7 +5035,7 @@
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>169</v>
       </c>
@@ -4925,7 +5060,7 @@
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>170</v>
       </c>
@@ -4950,7 +5085,7 @@
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>171</v>
       </c>
@@ -4975,7 +5110,7 @@
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>172</v>
       </c>
@@ -5000,7 +5135,7 @@
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>173</v>
       </c>
@@ -5025,7 +5160,7 @@
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>174</v>
       </c>
@@ -5050,7 +5185,7 @@
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>175</v>
       </c>
@@ -5075,7 +5210,7 @@
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>176</v>
       </c>
@@ -5100,7 +5235,7 @@
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>177</v>
       </c>
@@ -5125,7 +5260,7 @@
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>178</v>
       </c>
@@ -5150,7 +5285,7 @@
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>179</v>
       </c>
@@ -5175,7 +5310,7 @@
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>180</v>
       </c>
@@ -5200,7 +5335,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>181</v>
       </c>
@@ -5225,7 +5360,7 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>182</v>
       </c>
@@ -5250,7 +5385,7 @@
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>183</v>
       </c>
@@ -5275,7 +5410,7 @@
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>184</v>
       </c>
@@ -5300,7 +5435,7 @@
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>185</v>
       </c>
@@ -5325,7 +5460,7 @@
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>186</v>
       </c>
@@ -5350,7 +5485,7 @@
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>187</v>
       </c>
@@ -5375,7 +5510,7 @@
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>188</v>
       </c>
@@ -5400,7 +5535,7 @@
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>189</v>
       </c>
@@ -5425,7 +5560,7 @@
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>190</v>
       </c>
@@ -5450,7 +5585,7 @@
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>191</v>
       </c>
@@ -5475,7 +5610,7 @@
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>192</v>
       </c>
@@ -5500,7 +5635,7 @@
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>193</v>
       </c>
@@ -5525,7 +5660,7 @@
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>194</v>
       </c>
@@ -5550,7 +5685,7 @@
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>195</v>
       </c>
@@ -5575,7 +5710,7 @@
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>196</v>
       </c>
@@ -5600,7 +5735,7 @@
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>197</v>
       </c>
@@ -5625,7 +5760,7 @@
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>198</v>
       </c>
@@ -5650,7 +5785,7 @@
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
         <v>199</v>
       </c>
@@ -5675,7 +5810,7 @@
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>200</v>
       </c>
@@ -5700,7 +5835,7 @@
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>201</v>
       </c>
@@ -5725,7 +5860,7 @@
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>202</v>
       </c>
@@ -5750,7 +5885,7 @@
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
         <v>203</v>
       </c>
@@ -5775,7 +5910,7 @@
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>204</v>
       </c>
@@ -5800,7 +5935,7 @@
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
         <v>205</v>
       </c>
@@ -5825,7 +5960,7 @@
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>206</v>
       </c>
@@ -5850,7 +5985,7 @@
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
         <v>207</v>
       </c>
@@ -5875,7 +6010,7 @@
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>62</v>
       </c>
@@ -5900,7 +6035,7 @@
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
         <v>63</v>
       </c>
@@ -5925,7 +6060,7 @@
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>64</v>
       </c>
@@ -5950,7 +6085,7 @@
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
         <v>208</v>
       </c>
@@ -5975,7 +6110,7 @@
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>68</v>
       </c>
@@ -6000,7 +6135,7 @@
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
         <v>73</v>
       </c>
@@ -6025,7 +6160,7 @@
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>67</v>
       </c>
@@ -6050,7 +6185,7 @@
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
         <v>209</v>
       </c>
@@ -6075,7 +6210,7 @@
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>210</v>
       </c>
@@ -6100,7 +6235,7 @@
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
         <v>138</v>
       </c>
@@ -6125,7 +6260,7 @@
       <c r="S221" s="3"/>
       <c r="T221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>211</v>
       </c>
@@ -6150,7 +6285,7 @@
       <c r="S222" s="3"/>
       <c r="T222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
         <v>212</v>
       </c>
@@ -6175,7 +6310,7 @@
       <c r="S223" s="3"/>
       <c r="T223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>213</v>
       </c>
@@ -6197,7 +6332,7 @@
       <c r="S224" s="3"/>
       <c r="T224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
         <v>214</v>
       </c>
@@ -6219,7 +6354,7 @@
       <c r="S225" s="3"/>
       <c r="T225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>215</v>
       </c>
@@ -6241,7 +6376,7 @@
       <c r="S226" s="3"/>
       <c r="T226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
         <v>216</v>
       </c>
@@ -6263,7 +6398,7 @@
       <c r="S227" s="3"/>
       <c r="T227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>217</v>
       </c>
@@ -6285,7 +6420,7 @@
       <c r="S228" s="3"/>
       <c r="T228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
         <v>218</v>
       </c>
@@ -6307,7 +6442,7 @@
       <c r="S229" s="3"/>
       <c r="T229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>219</v>
       </c>
@@ -6329,7 +6464,7 @@
       <c r="S230" s="3"/>
       <c r="T230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>220</v>
       </c>
@@ -6351,7 +6486,7 @@
       <c r="S231" s="3"/>
       <c r="T231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>222</v>
       </c>
@@ -6373,7 +6508,7 @@
       <c r="S232" s="3"/>
       <c r="T232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>223</v>
       </c>
@@ -6395,7 +6530,7 @@
       <c r="S233" s="3"/>
       <c r="T233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>224</v>
       </c>
@@ -6417,7 +6552,7 @@
       <c r="S234" s="3"/>
       <c r="T234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>225</v>
       </c>
@@ -6439,7 +6574,7 @@
       <c r="S235" s="3"/>
       <c r="T235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>226</v>
       </c>
@@ -6461,7 +6596,7 @@
       <c r="S236" s="3"/>
       <c r="T236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>227</v>
       </c>
@@ -6483,7 +6618,7 @@
       <c r="S237" s="3"/>
       <c r="T237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>228</v>
       </c>
@@ -6505,7 +6640,7 @@
       <c r="S238" s="3"/>
       <c r="T238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>229</v>
       </c>
@@ -6527,7 +6662,7 @@
       <c r="S239" s="3"/>
       <c r="T239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>230</v>
       </c>
@@ -6549,7 +6684,7 @@
       <c r="S240" s="3"/>
       <c r="T240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>231</v>
       </c>
@@ -6571,7 +6706,7 @@
       <c r="S241" s="3"/>
       <c r="T241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>232</v>
       </c>
@@ -6593,7 +6728,7 @@
       <c r="S242" s="3"/>
       <c r="T242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>233</v>
       </c>
@@ -6615,7 +6750,7 @@
       <c r="S243" s="3"/>
       <c r="T243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>234</v>
       </c>
@@ -6637,7 +6772,7 @@
       <c r="S244" s="3"/>
       <c r="T244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>235</v>
       </c>
@@ -6659,7 +6794,7 @@
       <c r="S245" s="3"/>
       <c r="T245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>236</v>
       </c>
@@ -6681,7 +6816,7 @@
       <c r="S246" s="3"/>
       <c r="T246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>216</v>
       </c>
@@ -6703,7 +6838,7 @@
       <c r="S247" s="3"/>
       <c r="T247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>237</v>
       </c>
@@ -6725,7 +6860,7 @@
       <c r="S248" s="3"/>
       <c r="T248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>238</v>
       </c>
@@ -6747,7 +6882,7 @@
       <c r="S249" s="3"/>
       <c r="T249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>239</v>
       </c>
@@ -6769,7 +6904,7 @@
       <c r="S250" s="3"/>
       <c r="T250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>240</v>
       </c>
@@ -6791,7 +6926,7 @@
       <c r="S251" s="3"/>
       <c r="T251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>241</v>
       </c>
@@ -6813,7 +6948,7 @@
       <c r="S252" s="3"/>
       <c r="T252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>242</v>
       </c>
@@ -6835,7 +6970,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>243</v>
       </c>
@@ -6857,7 +6992,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>244</v>
       </c>
@@ -6879,7 +7014,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>245</v>
       </c>
@@ -6901,7 +7036,7 @@
       <c r="S256" s="3"/>
       <c r="T256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>246</v>
       </c>
@@ -6923,7 +7058,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>247</v>
       </c>
@@ -6945,7 +7080,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>248</v>
       </c>
@@ -6967,7 +7102,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>249</v>
       </c>
@@ -6989,7 +7124,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>250</v>
       </c>
@@ -7011,7 +7146,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>251</v>
       </c>
@@ -7033,7 +7168,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>252</v>
       </c>
@@ -7055,7 +7190,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>253</v>
       </c>
@@ -7077,7 +7212,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>254</v>
       </c>
@@ -7099,7 +7234,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>255</v>
       </c>
@@ -7121,7 +7256,7 @@
       <c r="S266" s="3"/>
       <c r="T266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>256</v>
       </c>
@@ -7143,7 +7278,7 @@
       <c r="S267" s="3"/>
       <c r="T267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>257</v>
       </c>
@@ -7165,7 +7300,7 @@
       <c r="S268" s="3"/>
       <c r="T268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>258</v>
       </c>
@@ -7187,7 +7322,7 @@
       <c r="S269" s="3"/>
       <c r="T269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>259</v>
       </c>
@@ -7209,7 +7344,7 @@
       <c r="S270" s="3"/>
       <c r="T270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>260</v>
       </c>
@@ -7231,7 +7366,7 @@
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>261</v>
       </c>
@@ -7253,7 +7388,7 @@
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>262</v>
       </c>
@@ -7275,7 +7410,7 @@
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>263</v>
       </c>
@@ -7297,7 +7432,7 @@
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>264</v>
       </c>
@@ -7319,7 +7454,7 @@
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>265</v>
       </c>
@@ -7341,7 +7476,7 @@
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>266</v>
       </c>
@@ -7363,7 +7498,7 @@
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>267</v>
       </c>
@@ -7385,7 +7520,7 @@
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>268</v>
       </c>
@@ -7407,7 +7542,7 @@
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>269</v>
       </c>
@@ -7429,7 +7564,7 @@
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>270</v>
       </c>
@@ -7451,7 +7586,7 @@
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>271</v>
       </c>
@@ -7473,7 +7608,7 @@
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>272</v>
       </c>
@@ -7495,7 +7630,7 @@
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>273</v>
       </c>
@@ -7517,7 +7652,7 @@
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>274</v>
       </c>
@@ -7539,7 +7674,7 @@
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
         <v>275</v>
       </c>
@@ -7561,7 +7696,7 @@
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>276</v>
       </c>
@@ -7583,7 +7718,7 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
         <v>277</v>
       </c>
@@ -7605,7 +7740,7 @@
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>278</v>
       </c>
@@ -7627,7 +7762,7 @@
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A290" s="7" t="s">
         <v>279</v>
       </c>
@@ -7649,7 +7784,7 @@
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>280</v>
       </c>
@@ -7671,7 +7806,7 @@
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="7" t="s">
         <v>281</v>
       </c>
@@ -7693,7 +7828,7 @@
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>282</v>
       </c>
@@ -7715,7 +7850,7 @@
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
         <v>283</v>
       </c>
@@ -7737,7 +7872,7 @@
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>284</v>
       </c>
@@ -7759,7 +7894,7 @@
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
         <v>285</v>
       </c>
@@ -7781,7 +7916,7 @@
       <c r="S296" s="3"/>
       <c r="T296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>286</v>
       </c>
@@ -7803,7 +7938,7 @@
       <c r="S297" s="3"/>
       <c r="T297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
         <v>287</v>
       </c>
@@ -7825,7 +7960,7 @@
       <c r="S298" s="3"/>
       <c r="T298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>288</v>
       </c>
@@ -7847,7 +7982,7 @@
       <c r="S299" s="3"/>
       <c r="T299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -7869,7 +8004,7 @@
       <c r="S300" s="3"/>
       <c r="T300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -7891,7 +8026,7 @@
       <c r="S301" s="3"/>
       <c r="T301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -7913,7 +8048,7 @@
       <c r="S302" s="3"/>
       <c r="T302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -7935,7 +8070,7 @@
       <c r="S303" s="3"/>
       <c r="T303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -7957,7 +8092,7 @@
       <c r="S304" s="3"/>
       <c r="T304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -7979,7 +8114,7 @@
       <c r="S305" s="3"/>
       <c r="T305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -8001,7 +8136,7 @@
       <c r="S306" s="3"/>
       <c r="T306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -8023,7 +8158,7 @@
       <c r="S307" s="3"/>
       <c r="T307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -8045,7 +8180,7 @@
       <c r="S308" s="3"/>
       <c r="T308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -8067,7 +8202,7 @@
       <c r="S309" s="3"/>
       <c r="T309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -8089,7 +8224,7 @@
       <c r="S310" s="3"/>
       <c r="T310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -8111,7 +8246,7 @@
       <c r="S311" s="3"/>
       <c r="T311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -8133,7 +8268,7 @@
       <c r="S312" s="3"/>
       <c r="T312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -8155,7 +8290,7 @@
       <c r="S313" s="3"/>
       <c r="T313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -8177,7 +8312,7 @@
       <c r="S314" s="3"/>
       <c r="T314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -8199,7 +8334,7 @@
       <c r="S315" s="3"/>
       <c r="T315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -8221,7 +8356,7 @@
       <c r="S316" s="3"/>
       <c r="T316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -8243,7 +8378,7 @@
       <c r="S317" s="3"/>
       <c r="T317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -8265,7 +8400,7 @@
       <c r="S318" s="3"/>
       <c r="T318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -8287,7 +8422,7 @@
       <c r="S319" s="3"/>
       <c r="T319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -8309,7 +8444,7 @@
       <c r="S320" s="3"/>
       <c r="T320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -8331,7 +8466,7 @@
       <c r="S321" s="3"/>
       <c r="T321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -8353,7 +8488,7 @@
       <c r="S322" s="3"/>
       <c r="T322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -8375,7 +8510,7 @@
       <c r="S323" s="3"/>
       <c r="T323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -8397,7 +8532,7 @@
       <c r="S324" s="3"/>
       <c r="T324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -8419,7 +8554,7 @@
       <c r="S325" s="3"/>
       <c r="T325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -8441,7 +8576,7 @@
       <c r="S326" s="3"/>
       <c r="T326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -8463,7 +8598,7 @@
       <c r="S327" s="3"/>
       <c r="T327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -8485,7 +8620,7 @@
       <c r="S328" s="3"/>
       <c r="T328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -8507,7 +8642,7 @@
       <c r="S329" s="3"/>
       <c r="T329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -8529,7 +8664,7 @@
       <c r="S330" s="3"/>
       <c r="T330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -8551,7 +8686,7 @@
       <c r="S331" s="3"/>
       <c r="T331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -8573,7 +8708,7 @@
       <c r="S332" s="3"/>
       <c r="T332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -8595,7 +8730,7 @@
       <c r="S333" s="3"/>
       <c r="T333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -8617,7 +8752,7 @@
       <c r="S334" s="3"/>
       <c r="T334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -8639,7 +8774,7 @@
       <c r="S335" s="3"/>
       <c r="T335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -8661,7 +8796,7 @@
       <c r="S336" s="3"/>
       <c r="T336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -8683,7 +8818,7 @@
       <c r="S337" s="3"/>
       <c r="T337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -8705,7 +8840,7 @@
       <c r="S338" s="3"/>
       <c r="T338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -8727,7 +8862,7 @@
       <c r="S339" s="3"/>
       <c r="T339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -8749,7 +8884,7 @@
       <c r="S340" s="3"/>
       <c r="T340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -8771,7 +8906,7 @@
       <c r="S341" s="3"/>
       <c r="T341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -8793,7 +8928,7 @@
       <c r="S342" s="3"/>
       <c r="T342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -8815,7 +8950,7 @@
       <c r="S343" s="3"/>
       <c r="T343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -8837,7 +8972,7 @@
       <c r="S344" s="3"/>
       <c r="T344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -8859,7 +8994,7 @@
       <c r="S345" s="3"/>
       <c r="T345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -8881,7 +9016,7 @@
       <c r="S346" s="3"/>
       <c r="T346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -8903,7 +9038,7 @@
       <c r="S347" s="3"/>
       <c r="T347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -8925,7 +9060,7 @@
       <c r="S348" s="3"/>
       <c r="T348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -8947,7 +9082,7 @@
       <c r="S349" s="3"/>
       <c r="T349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -8969,7 +9104,7 @@
       <c r="S350" s="3"/>
       <c r="T350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -8991,7 +9126,7 @@
       <c r="S351" s="3"/>
       <c r="T351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -9013,7 +9148,7 @@
       <c r="S352" s="3"/>
       <c r="T352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -9035,7 +9170,7 @@
       <c r="S353" s="3"/>
       <c r="T353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -9057,7 +9192,7 @@
       <c r="S354" s="3"/>
       <c r="T354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -9079,7 +9214,7 @@
       <c r="S355" s="3"/>
       <c r="T355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -9101,7 +9236,7 @@
       <c r="S356" s="3"/>
       <c r="T356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -9123,7 +9258,7 @@
       <c r="S357" s="3"/>
       <c r="T357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -9145,7 +9280,7 @@
       <c r="S358" s="3"/>
       <c r="T358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -9167,7 +9302,7 @@
       <c r="S359" s="3"/>
       <c r="T359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -9189,7 +9324,7 @@
       <c r="S360" s="3"/>
       <c r="T360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -9211,7 +9346,7 @@
       <c r="S361" s="3"/>
       <c r="T361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -9233,7 +9368,7 @@
       <c r="S362" s="3"/>
       <c r="T362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -9255,7 +9390,7 @@
       <c r="S363" s="3"/>
       <c r="T363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -9277,7 +9412,7 @@
       <c r="S364" s="3"/>
       <c r="T364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -9299,7 +9434,7 @@
       <c r="S365" s="3"/>
       <c r="T365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -9321,7 +9456,7 @@
       <c r="S366" s="3"/>
       <c r="T366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -9343,7 +9478,7 @@
       <c r="S367" s="3"/>
       <c r="T367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -9365,7 +9500,7 @@
       <c r="S368" s="3"/>
       <c r="T368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -9387,7 +9522,7 @@
       <c r="S369" s="3"/>
       <c r="T369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -9409,7 +9544,7 @@
       <c r="S370" s="3"/>
       <c r="T370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -9431,7 +9566,7 @@
       <c r="S371" s="3"/>
       <c r="T371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -9453,7 +9588,7 @@
       <c r="S372" s="3"/>
       <c r="T372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -9475,7 +9610,7 @@
       <c r="S373" s="3"/>
       <c r="T373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -9497,7 +9632,7 @@
       <c r="S374" s="3"/>
       <c r="T374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -9519,7 +9654,7 @@
       <c r="S375" s="3"/>
       <c r="T375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -9541,7 +9676,7 @@
       <c r="S376" s="3"/>
       <c r="T376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -9563,7 +9698,7 @@
       <c r="S377" s="3"/>
       <c r="T377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -9585,7 +9720,7 @@
       <c r="S378" s="3"/>
       <c r="T378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -9607,7 +9742,7 @@
       <c r="S379" s="3"/>
       <c r="T379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -9629,7 +9764,7 @@
       <c r="S380" s="3"/>
       <c r="T380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -9651,7 +9786,7 @@
       <c r="S381" s="3"/>
       <c r="T381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -9673,7 +9808,7 @@
       <c r="S382" s="3"/>
       <c r="T382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -9695,7 +9830,7 @@
       <c r="S383" s="3"/>
       <c r="T383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -9717,7 +9852,7 @@
       <c r="S384" s="3"/>
       <c r="T384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -9739,7 +9874,7 @@
       <c r="S385" s="3"/>
       <c r="T385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -9761,7 +9896,7 @@
       <c r="S386" s="3"/>
       <c r="T386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -9783,7 +9918,7 @@
       <c r="S387" s="3"/>
       <c r="T387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -9805,7 +9940,7 @@
       <c r="S388" s="3"/>
       <c r="T388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -9827,7 +9962,7 @@
       <c r="S389" s="3"/>
       <c r="T389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -9849,7 +9984,7 @@
       <c r="S390" s="3"/>
       <c r="T390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -9871,7 +10006,7 @@
       <c r="S391" s="3"/>
       <c r="T391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -9893,7 +10028,7 @@
       <c r="S392" s="3"/>
       <c r="T392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -9915,7 +10050,7 @@
       <c r="S393" s="3"/>
       <c r="T393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -9937,7 +10072,7 @@
       <c r="S394" s="3"/>
       <c r="T394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -9959,7 +10094,7 @@
       <c r="S395" s="3"/>
       <c r="T395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -9981,7 +10116,7 @@
       <c r="S396" s="3"/>
       <c r="T396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -10003,7 +10138,7 @@
       <c r="S397" s="3"/>
       <c r="T397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -10025,7 +10160,7 @@
       <c r="S398" s="3"/>
       <c r="T398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -10047,7 +10182,7 @@
       <c r="S399" s="3"/>
       <c r="T399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -10069,7 +10204,7 @@
       <c r="S400" s="3"/>
       <c r="T400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -10091,7 +10226,7 @@
       <c r="S401" s="3"/>
       <c r="T401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -10113,7 +10248,7 @@
       <c r="S402" s="3"/>
       <c r="T402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -10135,7 +10270,7 @@
       <c r="S403" s="3"/>
       <c r="T403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -10157,7 +10292,7 @@
       <c r="S404" s="3"/>
       <c r="T404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -10179,7 +10314,7 @@
       <c r="S405" s="3"/>
       <c r="T405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -10201,7 +10336,7 @@
       <c r="S406" s="3"/>
       <c r="T406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -10223,7 +10358,7 @@
       <c r="S407" s="3"/>
       <c r="T407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -10245,7 +10380,7 @@
       <c r="S408" s="3"/>
       <c r="T408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -10267,7 +10402,7 @@
       <c r="S409" s="3"/>
       <c r="T409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -10289,7 +10424,7 @@
       <c r="S410" s="3"/>
       <c r="T410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -10311,7 +10446,7 @@
       <c r="S411" s="3"/>
       <c r="T411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -10333,7 +10468,7 @@
       <c r="S412" s="3"/>
       <c r="T412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -10355,7 +10490,7 @@
       <c r="S413" s="3"/>
       <c r="T413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -10377,7 +10512,7 @@
       <c r="S414" s="3"/>
       <c r="T414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -10399,7 +10534,7 @@
       <c r="S415" s="3"/>
       <c r="T415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -10421,7 +10556,7 @@
       <c r="S416" s="3"/>
       <c r="T416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -10443,7 +10578,7 @@
       <c r="S417" s="3"/>
       <c r="T417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -10465,7 +10600,7 @@
       <c r="S418" s="3"/>
       <c r="T418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -10487,7 +10622,7 @@
       <c r="S419" s="3"/>
       <c r="T419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -10509,7 +10644,7 @@
       <c r="S420" s="3"/>
       <c r="T420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -10531,7 +10666,7 @@
       <c r="S421" s="3"/>
       <c r="T421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -10553,7 +10688,7 @@
       <c r="S422" s="3"/>
       <c r="T422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -10575,7 +10710,7 @@
       <c r="S423" s="3"/>
       <c r="T423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -10597,7 +10732,7 @@
       <c r="S424" s="3"/>
       <c r="T424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -10619,7 +10754,7 @@
       <c r="S425" s="3"/>
       <c r="T425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -10641,7 +10776,7 @@
       <c r="S426" s="3"/>
       <c r="T426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -10663,7 +10798,7 @@
       <c r="S427" s="3"/>
       <c r="T427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -10685,7 +10820,7 @@
       <c r="S428" s="3"/>
       <c r="T428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -10707,7 +10842,7 @@
       <c r="S429" s="3"/>
       <c r="T429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -10729,7 +10864,7 @@
       <c r="S430" s="3"/>
       <c r="T430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -10751,7 +10886,7 @@
       <c r="S431" s="3"/>
       <c r="T431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -10773,7 +10908,7 @@
       <c r="S432" s="3"/>
       <c r="T432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -10795,7 +10930,7 @@
       <c r="S433" s="3"/>
       <c r="T433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -10817,7 +10952,7 @@
       <c r="S434" s="3"/>
       <c r="T434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -10839,7 +10974,7 @@
       <c r="S435" s="3"/>
       <c r="T435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -10861,7 +10996,7 @@
       <c r="S436" s="3"/>
       <c r="T436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -10883,7 +11018,7 @@
       <c r="S437" s="3"/>
       <c r="T437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -10905,7 +11040,7 @@
       <c r="S438" s="3"/>
       <c r="T438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -10927,7 +11062,7 @@
       <c r="S439" s="3"/>
       <c r="T439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -10949,7 +11084,7 @@
       <c r="S440" s="3"/>
       <c r="T440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -10971,7 +11106,7 @@
       <c r="S441" s="3"/>
       <c r="T441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -10993,7 +11128,7 @@
       <c r="S442" s="3"/>
       <c r="T442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -11015,7 +11150,7 @@
       <c r="S443" s="3"/>
       <c r="T443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -11037,7 +11172,7 @@
       <c r="S444" s="3"/>
       <c r="T444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -11059,7 +11194,7 @@
       <c r="S445" s="3"/>
       <c r="T445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -11081,7 +11216,7 @@
       <c r="S446" s="3"/>
       <c r="T446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -11103,7 +11238,7 @@
       <c r="S447" s="3"/>
       <c r="T447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -11125,7 +11260,7 @@
       <c r="S448" s="3"/>
       <c r="T448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -11147,7 +11282,7 @@
       <c r="S449" s="3"/>
       <c r="T449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -11169,7 +11304,7 @@
       <c r="S450" s="3"/>
       <c r="T450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -11191,7 +11326,7 @@
       <c r="S451" s="3"/>
       <c r="T451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -11213,7 +11348,7 @@
       <c r="S452" s="3"/>
       <c r="T452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -11235,7 +11370,7 @@
       <c r="S453" s="3"/>
       <c r="T453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -11257,7 +11392,7 @@
       <c r="S454" s="3"/>
       <c r="T454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -11279,7 +11414,7 @@
       <c r="S455" s="3"/>
       <c r="T455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -11301,7 +11436,7 @@
       <c r="S456" s="3"/>
       <c r="T456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -11323,7 +11458,7 @@
       <c r="S457" s="3"/>
       <c r="T457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -11345,7 +11480,7 @@
       <c r="S458" s="3"/>
       <c r="T458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -11367,7 +11502,7 @@
       <c r="S459" s="3"/>
       <c r="T459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -11389,7 +11524,7 @@
       <c r="S460" s="3"/>
       <c r="T460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -11411,7 +11546,7 @@
       <c r="S461" s="3"/>
       <c r="T461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -11433,7 +11568,7 @@
       <c r="S462" s="3"/>
       <c r="T462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -11455,7 +11590,7 @@
       <c r="S463" s="3"/>
       <c r="T463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -11477,7 +11612,7 @@
       <c r="S464" s="3"/>
       <c r="T464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -11499,7 +11634,7 @@
       <c r="S465" s="3"/>
       <c r="T465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -11521,7 +11656,7 @@
       <c r="S466" s="3"/>
       <c r="T466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -11543,7 +11678,7 @@
       <c r="S467" s="3"/>
       <c r="T467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -11565,7 +11700,7 @@
       <c r="S468" s="3"/>
       <c r="T468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -11587,7 +11722,7 @@
       <c r="S469" s="3"/>
       <c r="T469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -11609,7 +11744,7 @@
       <c r="S470" s="3"/>
       <c r="T470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -11631,7 +11766,7 @@
       <c r="S471" s="3"/>
       <c r="T471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -11653,7 +11788,7 @@
       <c r="S472" s="3"/>
       <c r="T472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -11675,7 +11810,7 @@
       <c r="S473" s="3"/>
       <c r="T473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -11697,7 +11832,7 @@
       <c r="S474" s="3"/>
       <c r="T474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -11719,7 +11854,7 @@
       <c r="S475" s="3"/>
       <c r="T475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -11741,7 +11876,7 @@
       <c r="S476" s="3"/>
       <c r="T476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -11763,7 +11898,7 @@
       <c r="S477" s="3"/>
       <c r="T477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -11785,7 +11920,7 @@
       <c r="S478" s="3"/>
       <c r="T478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -11807,7 +11942,7 @@
       <c r="S479" s="3"/>
       <c r="T479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -11829,7 +11964,7 @@
       <c r="S480" s="3"/>
       <c r="T480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -11851,7 +11986,7 @@
       <c r="S481" s="3"/>
       <c r="T481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -11873,7 +12008,7 @@
       <c r="S482" s="3"/>
       <c r="T482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -11895,7 +12030,7 @@
       <c r="S483" s="3"/>
       <c r="T483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -11917,7 +12052,7 @@
       <c r="S484" s="3"/>
       <c r="T484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -11939,7 +12074,7 @@
       <c r="S485" s="3"/>
       <c r="T485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -11961,7 +12096,7 @@
       <c r="S486" s="3"/>
       <c r="T486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -11983,7 +12118,7 @@
       <c r="S487" s="3"/>
       <c r="T487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -12005,7 +12140,7 @@
       <c r="S488" s="3"/>
       <c r="T488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -12027,7 +12162,7 @@
       <c r="S489" s="3"/>
       <c r="T489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -12049,7 +12184,7 @@
       <c r="S490" s="3"/>
       <c r="T490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -12071,7 +12206,7 @@
       <c r="S491" s="3"/>
       <c r="T491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -12093,7 +12228,7 @@
       <c r="S492" s="3"/>
       <c r="T492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -12115,7 +12250,7 @@
       <c r="S493" s="3"/>
       <c r="T493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -12137,7 +12272,7 @@
       <c r="S494" s="3"/>
       <c r="T494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -12159,7 +12294,7 @@
       <c r="S495" s="3"/>
       <c r="T495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -12181,7 +12316,7 @@
       <c r="S496" s="3"/>
       <c r="T496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -12203,7 +12338,7 @@
       <c r="S497" s="3"/>
       <c r="T497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -12225,7 +12360,7 @@
       <c r="S498" s="3"/>
       <c r="T498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -12247,7 +12382,7 @@
       <c r="S499" s="3"/>
       <c r="T499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -12269,7 +12404,7 @@
       <c r="S500" s="3"/>
       <c r="T500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -12291,7 +12426,7 @@
       <c r="S501" s="3"/>
       <c r="T501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -12313,7 +12448,7 @@
       <c r="S502" s="3"/>
       <c r="T502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -12335,7 +12470,7 @@
       <c r="S503" s="3"/>
       <c r="T503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -12357,7 +12492,7 @@
       <c r="S504" s="3"/>
       <c r="T504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -12379,7 +12514,7 @@
       <c r="S505" s="3"/>
       <c r="T505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -12401,7 +12536,7 @@
       <c r="S506" s="3"/>
       <c r="T506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -12423,7 +12558,7 @@
       <c r="S507" s="3"/>
       <c r="T507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -12445,7 +12580,7 @@
       <c r="S508" s="3"/>
       <c r="T508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -12467,7 +12602,7 @@
       <c r="S509" s="3"/>
       <c r="T509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -12489,7 +12624,7 @@
       <c r="S510" s="3"/>
       <c r="T510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -12511,7 +12646,7 @@
       <c r="S511" s="3"/>
       <c r="T511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -12533,7 +12668,7 @@
       <c r="S512" s="3"/>
       <c r="T512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -12555,7 +12690,7 @@
       <c r="S513" s="3"/>
       <c r="T513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -12577,7 +12712,7 @@
       <c r="S514" s="3"/>
       <c r="T514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -12599,7 +12734,7 @@
       <c r="S515" s="3"/>
       <c r="T515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -12621,7 +12756,7 @@
       <c r="S516" s="3"/>
       <c r="T516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -12643,7 +12778,7 @@
       <c r="S517" s="3"/>
       <c r="T517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -12665,7 +12800,7 @@
       <c r="S518" s="3"/>
       <c r="T518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -12687,7 +12822,7 @@
       <c r="S519" s="3"/>
       <c r="T519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -12709,7 +12844,7 @@
       <c r="S520" s="3"/>
       <c r="T520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -12731,7 +12866,7 @@
       <c r="S521" s="3"/>
       <c r="T521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -12753,7 +12888,7 @@
       <c r="S522" s="3"/>
       <c r="T522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -12775,7 +12910,7 @@
       <c r="S523" s="3"/>
       <c r="T523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -12797,7 +12932,7 @@
       <c r="S524" s="3"/>
       <c r="T524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -12819,7 +12954,7 @@
       <c r="S525" s="3"/>
       <c r="T525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -12841,7 +12976,7 @@
       <c r="S526" s="3"/>
       <c r="T526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -12863,7 +12998,7 @@
       <c r="S527" s="3"/>
       <c r="T527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -12885,7 +13020,7 @@
       <c r="S528" s="3"/>
       <c r="T528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -12907,7 +13042,7 @@
       <c r="S529" s="3"/>
       <c r="T529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -12929,7 +13064,7 @@
       <c r="S530" s="3"/>
       <c r="T530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -12951,7 +13086,7 @@
       <c r="S531" s="3"/>
       <c r="T531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -12973,7 +13108,7 @@
       <c r="S532" s="3"/>
       <c r="T532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -12995,7 +13130,7 @@
       <c r="S533" s="3"/>
       <c r="T533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -13017,7 +13152,7 @@
       <c r="S534" s="3"/>
       <c r="T534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -13039,7 +13174,7 @@
       <c r="S535" s="3"/>
       <c r="T535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -13061,7 +13196,7 @@
       <c r="S536" s="3"/>
       <c r="T536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -13083,7 +13218,7 @@
       <c r="S537" s="3"/>
       <c r="T537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -13105,7 +13240,7 @@
       <c r="S538" s="3"/>
       <c r="T538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -13127,7 +13262,7 @@
       <c r="S539" s="3"/>
       <c r="T539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -13149,7 +13284,7 @@
       <c r="S540" s="3"/>
       <c r="T540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -13171,7 +13306,7 @@
       <c r="S541" s="3"/>
       <c r="T541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -13193,7 +13328,7 @@
       <c r="S542" s="3"/>
       <c r="T542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -13215,7 +13350,7 @@
       <c r="S543" s="3"/>
       <c r="T543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -13237,7 +13372,7 @@
       <c r="S544" s="3"/>
       <c r="T544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -13259,7 +13394,7 @@
       <c r="S545" s="3"/>
       <c r="T545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -13281,7 +13416,7 @@
       <c r="S546" s="3"/>
       <c r="T546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -13303,7 +13438,7 @@
       <c r="S547" s="3"/>
       <c r="T547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -13325,7 +13460,7 @@
       <c r="S548" s="3"/>
       <c r="T548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -13347,7 +13482,7 @@
       <c r="S549" s="3"/>
       <c r="T549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -13369,7 +13504,7 @@
       <c r="S550" s="3"/>
       <c r="T550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -13391,7 +13526,7 @@
       <c r="S551" s="3"/>
       <c r="T551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -13413,7 +13548,7 @@
       <c r="S552" s="3"/>
       <c r="T552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -13435,7 +13570,7 @@
       <c r="S553" s="3"/>
       <c r="T553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -13457,7 +13592,7 @@
       <c r="S554" s="3"/>
       <c r="T554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -13479,7 +13614,7 @@
       <c r="S555" s="3"/>
       <c r="T555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -13501,7 +13636,7 @@
       <c r="S556" s="3"/>
       <c r="T556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -13523,7 +13658,7 @@
       <c r="S557" s="3"/>
       <c r="T557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -13545,7 +13680,7 @@
       <c r="S558" s="3"/>
       <c r="T558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -13567,7 +13702,7 @@
       <c r="S559" s="3"/>
       <c r="T559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -13589,7 +13724,7 @@
       <c r="S560" s="3"/>
       <c r="T560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -13611,7 +13746,7 @@
       <c r="S561" s="3"/>
       <c r="T561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -13633,7 +13768,7 @@
       <c r="S562" s="3"/>
       <c r="T562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -13655,7 +13790,7 @@
       <c r="S563" s="3"/>
       <c r="T563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -13677,7 +13812,7 @@
       <c r="S564" s="3"/>
       <c r="T564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -13699,7 +13834,7 @@
       <c r="S565" s="3"/>
       <c r="T565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -13721,7 +13856,7 @@
       <c r="S566" s="3"/>
       <c r="T566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -13743,7 +13878,7 @@
       <c r="S567" s="3"/>
       <c r="T567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -13765,7 +13900,7 @@
       <c r="S568" s="3"/>
       <c r="T568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -13787,7 +13922,7 @@
       <c r="S569" s="3"/>
       <c r="T569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -13809,7 +13944,7 @@
       <c r="S570" s="3"/>
       <c r="T570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -13831,7 +13966,7 @@
       <c r="S571" s="3"/>
       <c r="T571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -13853,7 +13988,7 @@
       <c r="S572" s="3"/>
       <c r="T572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -13875,7 +14010,7 @@
       <c r="S573" s="3"/>
       <c r="T573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -13897,7 +14032,7 @@
       <c r="S574" s="3"/>
       <c r="T574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -13919,7 +14054,7 @@
       <c r="S575" s="3"/>
       <c r="T575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -13941,7 +14076,7 @@
       <c r="S576" s="3"/>
       <c r="T576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -13963,7 +14098,7 @@
       <c r="S577" s="3"/>
       <c r="T577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -13985,7 +14120,7 @@
       <c r="S578" s="3"/>
       <c r="T578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -14007,7 +14142,7 @@
       <c r="S579" s="3"/>
       <c r="T579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -14029,7 +14164,7 @@
       <c r="S580" s="3"/>
       <c r="T580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -14051,7 +14186,7 @@
       <c r="S581" s="3"/>
       <c r="T581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -14073,7 +14208,7 @@
       <c r="S582" s="3"/>
       <c r="T582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -14095,7 +14230,7 @@
       <c r="S583" s="3"/>
       <c r="T583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -14117,7 +14252,7 @@
       <c r="S584" s="3"/>
       <c r="T584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -14139,7 +14274,7 @@
       <c r="S585" s="3"/>
       <c r="T585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -14161,7 +14296,7 @@
       <c r="S586" s="3"/>
       <c r="T586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -14183,7 +14318,7 @@
       <c r="S587" s="3"/>
       <c r="T587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -14205,7 +14340,7 @@
       <c r="S588" s="3"/>
       <c r="T588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -14227,7 +14362,7 @@
       <c r="S589" s="3"/>
       <c r="T589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -14249,7 +14384,7 @@
       <c r="S590" s="3"/>
       <c r="T590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -14271,7 +14406,7 @@
       <c r="S591" s="3"/>
       <c r="T591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -14293,7 +14428,7 @@
       <c r="S592" s="3"/>
       <c r="T592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -14315,7 +14450,7 @@
       <c r="S593" s="3"/>
       <c r="T593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -14337,7 +14472,7 @@
       <c r="S594" s="3"/>
       <c r="T594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -14359,7 +14494,7 @@
       <c r="S595" s="3"/>
       <c r="T595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -14381,7 +14516,7 @@
       <c r="S596" s="3"/>
       <c r="T596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -14403,7 +14538,7 @@
       <c r="S597" s="3"/>
       <c r="T597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -14425,7 +14560,7 @@
       <c r="S598" s="3"/>
       <c r="T598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -14447,7 +14582,7 @@
       <c r="S599" s="3"/>
       <c r="T599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -14469,7 +14604,7 @@
       <c r="S600" s="3"/>
       <c r="T600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -14491,7 +14626,7 @@
       <c r="S601" s="3"/>
       <c r="T601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -14513,7 +14648,7 @@
       <c r="S602" s="3"/>
       <c r="T602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -14535,7 +14670,7 @@
       <c r="S603" s="3"/>
       <c r="T603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -14557,7 +14692,7 @@
       <c r="S604" s="3"/>
       <c r="T604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -14579,7 +14714,7 @@
       <c r="S605" s="3"/>
       <c r="T605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -14601,7 +14736,7 @@
       <c r="S606" s="3"/>
       <c r="T606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -14623,7 +14758,7 @@
       <c r="S607" s="3"/>
       <c r="T607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -14645,7 +14780,7 @@
       <c r="S608" s="3"/>
       <c r="T608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -14667,7 +14802,7 @@
       <c r="S609" s="3"/>
       <c r="T609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -14689,7 +14824,7 @@
       <c r="S610" s="3"/>
       <c r="T610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -14711,7 +14846,7 @@
       <c r="S611" s="3"/>
       <c r="T611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -14733,7 +14868,7 @@
       <c r="S612" s="3"/>
       <c r="T612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -14755,7 +14890,7 @@
       <c r="S613" s="3"/>
       <c r="T613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -14777,7 +14912,7 @@
       <c r="S614" s="3"/>
       <c r="T614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -14799,7 +14934,7 @@
       <c r="S615" s="3"/>
       <c r="T615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -14821,7 +14956,7 @@
       <c r="S616" s="3"/>
       <c r="T616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -14843,7 +14978,7 @@
       <c r="S617" s="3"/>
       <c r="T617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -14865,7 +15000,7 @@
       <c r="S618" s="3"/>
       <c r="T618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -14887,7 +15022,7 @@
       <c r="S619" s="3"/>
       <c r="T619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -14909,7 +15044,7 @@
       <c r="S620" s="3"/>
       <c r="T620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -14931,7 +15066,7 @@
       <c r="S621" s="3"/>
       <c r="T621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -14953,7 +15088,7 @@
       <c r="S622" s="3"/>
       <c r="T622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -14975,7 +15110,7 @@
       <c r="S623" s="3"/>
       <c r="T623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -14997,7 +15132,7 @@
       <c r="S624" s="3"/>
       <c r="T624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -15019,7 +15154,7 @@
       <c r="S625" s="3"/>
       <c r="T625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -15041,7 +15176,7 @@
       <c r="S626" s="3"/>
       <c r="T626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -15063,7 +15198,7 @@
       <c r="S627" s="3"/>
       <c r="T627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -15085,7 +15220,7 @@
       <c r="S628" s="3"/>
       <c r="T628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -15107,7 +15242,7 @@
       <c r="S629" s="3"/>
       <c r="T629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -15129,7 +15264,7 @@
       <c r="S630" s="3"/>
       <c r="T630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -15151,7 +15286,7 @@
       <c r="S631" s="3"/>
       <c r="T631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -15173,7 +15308,7 @@
       <c r="S632" s="3"/>
       <c r="T632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -15195,7 +15330,7 @@
       <c r="S633" s="3"/>
       <c r="T633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -15217,7 +15352,7 @@
       <c r="S634" s="3"/>
       <c r="T634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -15239,7 +15374,7 @@
       <c r="S635" s="3"/>
       <c r="T635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -15261,7 +15396,7 @@
       <c r="S636" s="3"/>
       <c r="T636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -15283,7 +15418,7 @@
       <c r="S637" s="3"/>
       <c r="T637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -15305,7 +15440,7 @@
       <c r="S638" s="3"/>
       <c r="T638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -15327,7 +15462,7 @@
       <c r="S639" s="3"/>
       <c r="T639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -15349,7 +15484,7 @@
       <c r="S640" s="3"/>
       <c r="T640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -15371,7 +15506,7 @@
       <c r="S641" s="3"/>
       <c r="T641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -15393,7 +15528,7 @@
       <c r="S642" s="3"/>
       <c r="T642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -15415,7 +15550,7 @@
       <c r="S643" s="3"/>
       <c r="T643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -15437,7 +15572,7 @@
       <c r="S644" s="3"/>
       <c r="T644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -15459,7 +15594,7 @@
       <c r="S645" s="3"/>
       <c r="T645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -15481,7 +15616,7 @@
       <c r="S646" s="3"/>
       <c r="T646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -15503,7 +15638,7 @@
       <c r="S647" s="3"/>
       <c r="T647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -15525,7 +15660,7 @@
       <c r="S648" s="3"/>
       <c r="T648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -15547,7 +15682,7 @@
       <c r="S649" s="3"/>
       <c r="T649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -15569,7 +15704,7 @@
       <c r="S650" s="3"/>
       <c r="T650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -15591,7 +15726,7 @@
       <c r="S651" s="3"/>
       <c r="T651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -15613,7 +15748,7 @@
       <c r="S652" s="3"/>
       <c r="T652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -15635,7 +15770,7 @@
       <c r="S653" s="3"/>
       <c r="T653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -15657,7 +15792,7 @@
       <c r="S654" s="3"/>
       <c r="T654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -15679,7 +15814,7 @@
       <c r="S655" s="3"/>
       <c r="T655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -15701,7 +15836,7 @@
       <c r="S656" s="3"/>
       <c r="T656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -15723,7 +15858,7 @@
       <c r="S657" s="3"/>
       <c r="T657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -15745,7 +15880,7 @@
       <c r="S658" s="3"/>
       <c r="T658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -15767,7 +15902,7 @@
       <c r="S659" s="3"/>
       <c r="T659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -15789,7 +15924,7 @@
       <c r="S660" s="3"/>
       <c r="T660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -15811,7 +15946,7 @@
       <c r="S661" s="3"/>
       <c r="T661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -15833,7 +15968,7 @@
       <c r="S662" s="3"/>
       <c r="T662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -15855,7 +15990,7 @@
       <c r="S663" s="3"/>
       <c r="T663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -15877,7 +16012,7 @@
       <c r="S664" s="3"/>
       <c r="T664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -15899,7 +16034,7 @@
       <c r="S665" s="3"/>
       <c r="T665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -15921,7 +16056,7 @@
       <c r="S666" s="3"/>
       <c r="T666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -15943,7 +16078,7 @@
       <c r="S667" s="3"/>
       <c r="T667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -15965,7 +16100,7 @@
       <c r="S668" s="3"/>
       <c r="T668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -15987,7 +16122,7 @@
       <c r="S669" s="3"/>
       <c r="T669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -16009,7 +16144,7 @@
       <c r="S670" s="3"/>
       <c r="T670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -16031,7 +16166,7 @@
       <c r="S671" s="3"/>
       <c r="T671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -16053,7 +16188,7 @@
       <c r="S672" s="3"/>
       <c r="T672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -16075,7 +16210,7 @@
       <c r="S673" s="3"/>
       <c r="T673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -16097,7 +16232,7 @@
       <c r="S674" s="3"/>
       <c r="T674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -16119,7 +16254,7 @@
       <c r="S675" s="3"/>
       <c r="T675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -16141,7 +16276,7 @@
       <c r="S676" s="3"/>
       <c r="T676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -16163,7 +16298,7 @@
       <c r="S677" s="3"/>
       <c r="T677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -16185,7 +16320,7 @@
       <c r="S678" s="3"/>
       <c r="T678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -16207,7 +16342,7 @@
       <c r="S679" s="3"/>
       <c r="T679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -16229,7 +16364,7 @@
       <c r="S680" s="3"/>
       <c r="T680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -16251,7 +16386,7 @@
       <c r="S681" s="3"/>
       <c r="T681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -16273,7 +16408,7 @@
       <c r="S682" s="3"/>
       <c r="T682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -16295,7 +16430,7 @@
       <c r="S683" s="3"/>
       <c r="T683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -16317,7 +16452,7 @@
       <c r="S684" s="3"/>
       <c r="T684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -16339,7 +16474,7 @@
       <c r="S685" s="3"/>
       <c r="T685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -16361,7 +16496,7 @@
       <c r="S686" s="3"/>
       <c r="T686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -16383,7 +16518,7 @@
       <c r="S687" s="3"/>
       <c r="T687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -16405,7 +16540,7 @@
       <c r="S688" s="3"/>
       <c r="T688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -16427,7 +16562,7 @@
       <c r="S689" s="3"/>
       <c r="T689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -16449,7 +16584,7 @@
       <c r="S690" s="3"/>
       <c r="T690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -16471,7 +16606,7 @@
       <c r="S691" s="3"/>
       <c r="T691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -16493,7 +16628,7 @@
       <c r="S692" s="3"/>
       <c r="T692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -16515,7 +16650,7 @@
       <c r="S693" s="3"/>
       <c r="T693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -16537,7 +16672,7 @@
       <c r="S694" s="3"/>
       <c r="T694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -16559,7 +16694,7 @@
       <c r="S695" s="3"/>
       <c r="T695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -16581,7 +16716,7 @@
       <c r="S696" s="3"/>
       <c r="T696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -16603,7 +16738,7 @@
       <c r="S697" s="3"/>
       <c r="T697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -16625,7 +16760,7 @@
       <c r="S698" s="3"/>
       <c r="T698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -16647,7 +16782,7 @@
       <c r="S699" s="3"/>
       <c r="T699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -16669,7 +16804,7 @@
       <c r="S700" s="3"/>
       <c r="T700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -16691,7 +16826,7 @@
       <c r="S701" s="3"/>
       <c r="T701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -16713,7 +16848,7 @@
       <c r="S702" s="3"/>
       <c r="T702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -16735,7 +16870,7 @@
       <c r="S703" s="3"/>
       <c r="T703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -16757,7 +16892,7 @@
       <c r="S704" s="3"/>
       <c r="T704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -16779,7 +16914,7 @@
       <c r="S705" s="3"/>
       <c r="T705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -16801,7 +16936,7 @@
       <c r="S706" s="3"/>
       <c r="T706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -16823,7 +16958,7 @@
       <c r="S707" s="3"/>
       <c r="T707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -16845,7 +16980,7 @@
       <c r="S708" s="3"/>
       <c r="T708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -16867,7 +17002,7 @@
       <c r="S709" s="3"/>
       <c r="T709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -16889,7 +17024,7 @@
       <c r="S710" s="3"/>
       <c r="T710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -16911,7 +17046,7 @@
       <c r="S711" s="3"/>
       <c r="T711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -16933,7 +17068,7 @@
       <c r="S712" s="3"/>
       <c r="T712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -16955,7 +17090,7 @@
       <c r="S713" s="3"/>
       <c r="T713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -16977,7 +17112,7 @@
       <c r="S714" s="3"/>
       <c r="T714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -16999,7 +17134,7 @@
       <c r="S715" s="3"/>
       <c r="T715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -17021,7 +17156,7 @@
       <c r="S716" s="3"/>
       <c r="T716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -17043,7 +17178,7 @@
       <c r="S717" s="3"/>
       <c r="T717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -17065,7 +17200,7 @@
       <c r="S718" s="3"/>
       <c r="T718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -17087,7 +17222,7 @@
       <c r="S719" s="3"/>
       <c r="T719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -17109,7 +17244,7 @@
       <c r="S720" s="3"/>
       <c r="T720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -17131,7 +17266,7 @@
       <c r="S721" s="3"/>
       <c r="T721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -17153,7 +17288,7 @@
       <c r="S722" s="3"/>
       <c r="T722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -17175,7 +17310,7 @@
       <c r="S723" s="3"/>
       <c r="T723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -17197,7 +17332,7 @@
       <c r="S724" s="3"/>
       <c r="T724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -17219,7 +17354,7 @@
       <c r="S725" s="3"/>
       <c r="T725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -17241,7 +17376,7 @@
       <c r="S726" s="3"/>
       <c r="T726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -17263,7 +17398,7 @@
       <c r="S727" s="3"/>
       <c r="T727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -17285,7 +17420,7 @@
       <c r="S728" s="3"/>
       <c r="T728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -17307,7 +17442,7 @@
       <c r="S729" s="3"/>
       <c r="T729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -17329,7 +17464,7 @@
       <c r="S730" s="3"/>
       <c r="T730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -17351,7 +17486,7 @@
       <c r="S731" s="3"/>
       <c r="T731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -17373,7 +17508,7 @@
       <c r="S732" s="3"/>
       <c r="T732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -17395,7 +17530,7 @@
       <c r="S733" s="3"/>
       <c r="T733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -17417,7 +17552,7 @@
       <c r="S734" s="3"/>
       <c r="T734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -17439,7 +17574,7 @@
       <c r="S735" s="3"/>
       <c r="T735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -17461,7 +17596,7 @@
       <c r="S736" s="3"/>
       <c r="T736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -17483,7 +17618,7 @@
       <c r="S737" s="3"/>
       <c r="T737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -17505,7 +17640,7 @@
       <c r="S738" s="3"/>
       <c r="T738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -17527,7 +17662,7 @@
       <c r="S739" s="3"/>
       <c r="T739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -17549,7 +17684,7 @@
       <c r="S740" s="3"/>
       <c r="T740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -17571,7 +17706,7 @@
       <c r="S741" s="3"/>
       <c r="T741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -17593,7 +17728,7 @@
       <c r="S742" s="3"/>
       <c r="T742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -17615,7 +17750,7 @@
       <c r="S743" s="3"/>
       <c r="T743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -17637,7 +17772,7 @@
       <c r="S744" s="3"/>
       <c r="T744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -17659,7 +17794,7 @@
       <c r="S745" s="3"/>
       <c r="T745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -17681,7 +17816,7 @@
       <c r="S746" s="3"/>
       <c r="T746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -17703,7 +17838,7 @@
       <c r="S747" s="3"/>
       <c r="T747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -17725,7 +17860,7 @@
       <c r="S748" s="3"/>
       <c r="T748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -17747,7 +17882,7 @@
       <c r="S749" s="3"/>
       <c r="T749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -17769,7 +17904,7 @@
       <c r="S750" s="3"/>
       <c r="T750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -17791,7 +17926,7 @@
       <c r="S751" s="3"/>
       <c r="T751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -17813,7 +17948,7 @@
       <c r="S752" s="3"/>
       <c r="T752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -17835,7 +17970,7 @@
       <c r="S753" s="3"/>
       <c r="T753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -17857,7 +17992,7 @@
       <c r="S754" s="3"/>
       <c r="T754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -17879,7 +18014,7 @@
       <c r="S755" s="3"/>
       <c r="T755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -17901,7 +18036,7 @@
       <c r="S756" s="3"/>
       <c r="T756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -17923,7 +18058,7 @@
       <c r="S757" s="3"/>
       <c r="T757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -17945,7 +18080,7 @@
       <c r="S758" s="3"/>
       <c r="T758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -17967,7 +18102,7 @@
       <c r="S759" s="3"/>
       <c r="T759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -17989,7 +18124,7 @@
       <c r="S760" s="3"/>
       <c r="T760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -18011,7 +18146,7 @@
       <c r="S761" s="3"/>
       <c r="T761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -18033,7 +18168,7 @@
       <c r="S762" s="3"/>
       <c r="T762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -18055,7 +18190,7 @@
       <c r="S763" s="3"/>
       <c r="T763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -18077,7 +18212,7 @@
       <c r="S764" s="3"/>
       <c r="T764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -18099,7 +18234,7 @@
       <c r="S765" s="3"/>
       <c r="T765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -18121,7 +18256,7 @@
       <c r="S766" s="3"/>
       <c r="T766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -18143,7 +18278,7 @@
       <c r="S767" s="3"/>
       <c r="T767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -18165,7 +18300,7 @@
       <c r="S768" s="3"/>
       <c r="T768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -18187,7 +18322,7 @@
       <c r="S769" s="3"/>
       <c r="T769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -18209,7 +18344,7 @@
       <c r="S770" s="3"/>
       <c r="T770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -18231,7 +18366,7 @@
       <c r="S771" s="3"/>
       <c r="T771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -18253,7 +18388,7 @@
       <c r="S772" s="3"/>
       <c r="T772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -18275,7 +18410,7 @@
       <c r="S773" s="3"/>
       <c r="T773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -18297,7 +18432,7 @@
       <c r="S774" s="3"/>
       <c r="T774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -18319,7 +18454,7 @@
       <c r="S775" s="3"/>
       <c r="T775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -18341,7 +18476,7 @@
       <c r="S776" s="3"/>
       <c r="T776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -18363,7 +18498,7 @@
       <c r="S777" s="3"/>
       <c r="T777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -18385,7 +18520,7 @@
       <c r="S778" s="3"/>
       <c r="T778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -18407,7 +18542,7 @@
       <c r="S779" s="3"/>
       <c r="T779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -18429,7 +18564,7 @@
       <c r="S780" s="3"/>
       <c r="T780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -18451,7 +18586,7 @@
       <c r="S781" s="3"/>
       <c r="T781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -18473,7 +18608,7 @@
       <c r="S782" s="3"/>
       <c r="T782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -18495,7 +18630,7 @@
       <c r="S783" s="3"/>
       <c r="T783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -18517,7 +18652,7 @@
       <c r="S784" s="3"/>
       <c r="T784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -18539,7 +18674,7 @@
       <c r="S785" s="3"/>
       <c r="T785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -18561,7 +18696,7 @@
       <c r="S786" s="3"/>
       <c r="T786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -18583,7 +18718,7 @@
       <c r="S787" s="3"/>
       <c r="T787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -18605,7 +18740,7 @@
       <c r="S788" s="3"/>
       <c r="T788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -18627,7 +18762,7 @@
       <c r="S789" s="3"/>
       <c r="T789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -18649,7 +18784,7 @@
       <c r="S790" s="3"/>
       <c r="T790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -18671,7 +18806,7 @@
       <c r="S791" s="3"/>
       <c r="T791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -18693,7 +18828,7 @@
       <c r="S792" s="3"/>
       <c r="T792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -18715,7 +18850,7 @@
       <c r="S793" s="3"/>
       <c r="T793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -18737,7 +18872,7 @@
       <c r="S794" s="3"/>
       <c r="T794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -18759,7 +18894,7 @@
       <c r="S795" s="3"/>
       <c r="T795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -18781,7 +18916,7 @@
       <c r="S796" s="3"/>
       <c r="T796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -18803,7 +18938,7 @@
       <c r="S797" s="3"/>
       <c r="T797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -18825,7 +18960,7 @@
       <c r="S798" s="3"/>
       <c r="T798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -18847,7 +18982,7 @@
       <c r="S799" s="3"/>
       <c r="T799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -18869,7 +19004,7 @@
       <c r="S800" s="3"/>
       <c r="T800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -18891,7 +19026,7 @@
       <c r="S801" s="3"/>
       <c r="T801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -18913,7 +19048,7 @@
       <c r="S802" s="3"/>
       <c r="T802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -18935,7 +19070,7 @@
       <c r="S803" s="3"/>
       <c r="T803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -18957,7 +19092,7 @@
       <c r="S804" s="3"/>
       <c r="T804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -18979,7 +19114,7 @@
       <c r="S805" s="3"/>
       <c r="T805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -19001,7 +19136,7 @@
       <c r="S806" s="3"/>
       <c r="T806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -19023,7 +19158,7 @@
       <c r="S807" s="3"/>
       <c r="T807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -19045,7 +19180,7 @@
       <c r="S808" s="3"/>
       <c r="T808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -19067,7 +19202,7 @@
       <c r="S809" s="3"/>
       <c r="T809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -19089,7 +19224,7 @@
       <c r="S810" s="3"/>
       <c r="T810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -19111,7 +19246,7 @@
       <c r="S811" s="3"/>
       <c r="T811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -19133,7 +19268,7 @@
       <c r="S812" s="3"/>
       <c r="T812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -19155,7 +19290,7 @@
       <c r="S813" s="3"/>
       <c r="T813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -19177,7 +19312,7 @@
       <c r="S814" s="3"/>
       <c r="T814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -19199,7 +19334,7 @@
       <c r="S815" s="3"/>
       <c r="T815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -19221,7 +19356,7 @@
       <c r="S816" s="3"/>
       <c r="T816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -19243,7 +19378,7 @@
       <c r="S817" s="3"/>
       <c r="T817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -19265,7 +19400,7 @@
       <c r="S818" s="3"/>
       <c r="T818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -19287,7 +19422,7 @@
       <c r="S819" s="3"/>
       <c r="T819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -19309,7 +19444,7 @@
       <c r="S820" s="3"/>
       <c r="T820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -19331,7 +19466,7 @@
       <c r="S821" s="3"/>
       <c r="T821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -19353,7 +19488,7 @@
       <c r="S822" s="3"/>
       <c r="T822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -19375,7 +19510,7 @@
       <c r="S823" s="3"/>
       <c r="T823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -19397,7 +19532,7 @@
       <c r="S824" s="3"/>
       <c r="T824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -19419,7 +19554,7 @@
       <c r="S825" s="3"/>
       <c r="T825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -19441,7 +19576,7 @@
       <c r="S826" s="3"/>
       <c r="T826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -19463,7 +19598,7 @@
       <c r="S827" s="3"/>
       <c r="T827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -19485,7 +19620,7 @@
       <c r="S828" s="3"/>
       <c r="T828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -19507,7 +19642,7 @@
       <c r="S829" s="3"/>
       <c r="T829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -19529,7 +19664,7 @@
       <c r="S830" s="3"/>
       <c r="T830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -19551,7 +19686,7 @@
       <c r="S831" s="3"/>
       <c r="T831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -19573,7 +19708,7 @@
       <c r="S832" s="3"/>
       <c r="T832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -19595,7 +19730,7 @@
       <c r="S833" s="3"/>
       <c r="T833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -19617,7 +19752,7 @@
       <c r="S834" s="3"/>
       <c r="T834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -19639,7 +19774,7 @@
       <c r="S835" s="3"/>
       <c r="T835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -19661,7 +19796,7 @@
       <c r="S836" s="3"/>
       <c r="T836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -19683,7 +19818,7 @@
       <c r="S837" s="3"/>
       <c r="T837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -19705,7 +19840,7 @@
       <c r="S838" s="3"/>
       <c r="T838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -19727,7 +19862,7 @@
       <c r="S839" s="3"/>
       <c r="T839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -19749,7 +19884,7 @@
       <c r="S840" s="3"/>
       <c r="T840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -19771,7 +19906,7 @@
       <c r="S841" s="3"/>
       <c r="T841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -19793,7 +19928,7 @@
       <c r="S842" s="3"/>
       <c r="T842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -19815,7 +19950,7 @@
       <c r="S843" s="3"/>
       <c r="T843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -19837,7 +19972,7 @@
       <c r="S844" s="3"/>
       <c r="T844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -19859,7 +19994,7 @@
       <c r="S845" s="3"/>
       <c r="T845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -19881,7 +20016,7 @@
       <c r="S846" s="3"/>
       <c r="T846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -19903,7 +20038,7 @@
       <c r="S847" s="3"/>
       <c r="T847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -19925,7 +20060,7 @@
       <c r="S848" s="3"/>
       <c r="T848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -19947,7 +20082,7 @@
       <c r="S849" s="3"/>
       <c r="T849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -19969,7 +20104,7 @@
       <c r="S850" s="3"/>
       <c r="T850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -19991,7 +20126,7 @@
       <c r="S851" s="3"/>
       <c r="T851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -20013,7 +20148,7 @@
       <c r="S852" s="3"/>
       <c r="T852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -20035,7 +20170,7 @@
       <c r="S853" s="3"/>
       <c r="T853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -20057,7 +20192,7 @@
       <c r="S854" s="3"/>
       <c r="T854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -20079,7 +20214,7 @@
       <c r="S855" s="3"/>
       <c r="T855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -20101,7 +20236,7 @@
       <c r="S856" s="3"/>
       <c r="T856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -20123,7 +20258,7 @@
       <c r="S857" s="3"/>
       <c r="T857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -20145,7 +20280,7 @@
       <c r="S858" s="3"/>
       <c r="T858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -20167,7 +20302,7 @@
       <c r="S859" s="3"/>
       <c r="T859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -20189,7 +20324,7 @@
       <c r="S860" s="3"/>
       <c r="T860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -20211,7 +20346,7 @@
       <c r="S861" s="3"/>
       <c r="T861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -20233,7 +20368,7 @@
       <c r="S862" s="3"/>
       <c r="T862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -20255,7 +20390,7 @@
       <c r="S863" s="3"/>
       <c r="T863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -20277,7 +20412,7 @@
       <c r="S864" s="3"/>
       <c r="T864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -20299,7 +20434,7 @@
       <c r="S865" s="3"/>
       <c r="T865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -20321,7 +20456,7 @@
       <c r="S866" s="3"/>
       <c r="T866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -20343,7 +20478,7 @@
       <c r="S867" s="3"/>
       <c r="T867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -20365,7 +20500,7 @@
       <c r="S868" s="3"/>
       <c r="T868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -20387,7 +20522,7 @@
       <c r="S869" s="3"/>
       <c r="T869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -20409,7 +20544,7 @@
       <c r="S870" s="3"/>
       <c r="T870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -20431,7 +20566,7 @@
       <c r="S871" s="3"/>
       <c r="T871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -20453,7 +20588,7 @@
       <c r="S872" s="3"/>
       <c r="T872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -20475,7 +20610,7 @@
       <c r="S873" s="3"/>
       <c r="T873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -20497,7 +20632,7 @@
       <c r="S874" s="3"/>
       <c r="T874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -20519,7 +20654,7 @@
       <c r="S875" s="3"/>
       <c r="T875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -20541,7 +20676,7 @@
       <c r="S876" s="3"/>
       <c r="T876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -20563,7 +20698,7 @@
       <c r="S877" s="3"/>
       <c r="T877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -20585,7 +20720,7 @@
       <c r="S878" s="3"/>
       <c r="T878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -20607,7 +20742,7 @@
       <c r="S879" s="3"/>
       <c r="T879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -20629,7 +20764,7 @@
       <c r="S880" s="3"/>
       <c r="T880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -20651,7 +20786,7 @@
       <c r="S881" s="3"/>
       <c r="T881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -20673,7 +20808,7 @@
       <c r="S882" s="3"/>
       <c r="T882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -20695,7 +20830,7 @@
       <c r="S883" s="3"/>
       <c r="T883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -20717,7 +20852,7 @@
       <c r="S884" s="3"/>
       <c r="T884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -20739,7 +20874,7 @@
       <c r="S885" s="3"/>
       <c r="T885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -20761,7 +20896,7 @@
       <c r="S886" s="3"/>
       <c r="T886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -20783,7 +20918,7 @@
       <c r="S887" s="3"/>
       <c r="T887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -20805,7 +20940,7 @@
       <c r="S888" s="3"/>
       <c r="T888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -20827,7 +20962,7 @@
       <c r="S889" s="3"/>
       <c r="T889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -20849,7 +20984,7 @@
       <c r="S890" s="3"/>
       <c r="T890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -20871,7 +21006,7 @@
       <c r="S891" s="3"/>
       <c r="T891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -20893,7 +21028,7 @@
       <c r="S892" s="3"/>
       <c r="T892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -20915,7 +21050,7 @@
       <c r="S893" s="3"/>
       <c r="T893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -20937,7 +21072,7 @@
       <c r="S894" s="3"/>
       <c r="T894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -20959,7 +21094,7 @@
       <c r="S895" s="3"/>
       <c r="T895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -20981,7 +21116,7 @@
       <c r="S896" s="3"/>
       <c r="T896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -21003,7 +21138,7 @@
       <c r="S897" s="3"/>
       <c r="T897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -21025,7 +21160,7 @@
       <c r="S898" s="3"/>
       <c r="T898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -21047,7 +21182,7 @@
       <c r="S899" s="3"/>
       <c r="T899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -21069,7 +21204,7 @@
       <c r="S900" s="3"/>
       <c r="T900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -21091,7 +21226,7 @@
       <c r="S901" s="3"/>
       <c r="T901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -21113,7 +21248,7 @@
       <c r="S902" s="3"/>
       <c r="T902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -21135,7 +21270,7 @@
       <c r="S903" s="3"/>
       <c r="T903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -21157,7 +21292,7 @@
       <c r="S904" s="3"/>
       <c r="T904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -21179,7 +21314,7 @@
       <c r="S905" s="3"/>
       <c r="T905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -21201,7 +21336,7 @@
       <c r="S906" s="3"/>
       <c r="T906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -21223,7 +21358,7 @@
       <c r="S907" s="3"/>
       <c r="T907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -21245,7 +21380,7 @@
       <c r="S908" s="3"/>
       <c r="T908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -21267,7 +21402,7 @@
       <c r="S909" s="3"/>
       <c r="T909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -21289,7 +21424,7 @@
       <c r="S910" s="3"/>
       <c r="T910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -21311,7 +21446,7 @@
       <c r="S911" s="3"/>
       <c r="T911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -21333,7 +21468,7 @@
       <c r="S912" s="3"/>
       <c r="T912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -21355,7 +21490,7 @@
       <c r="S913" s="3"/>
       <c r="T913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -21377,7 +21512,7 @@
       <c r="S914" s="3"/>
       <c r="T914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -21399,7 +21534,7 @@
       <c r="S915" s="3"/>
       <c r="T915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -21421,7 +21556,7 @@
       <c r="S916" s="3"/>
       <c r="T916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -21443,7 +21578,7 @@
       <c r="S917" s="3"/>
       <c r="T917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -21465,7 +21600,7 @@
       <c r="S918" s="3"/>
       <c r="T918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -21487,7 +21622,7 @@
       <c r="S919" s="3"/>
       <c r="T919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -21509,7 +21644,7 @@
       <c r="S920" s="3"/>
       <c r="T920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -21531,7 +21666,7 @@
       <c r="S921" s="3"/>
       <c r="T921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -21553,7 +21688,7 @@
       <c r="S922" s="3"/>
       <c r="T922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -21575,7 +21710,7 @@
       <c r="S923" s="3"/>
       <c r="T923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -21597,7 +21732,7 @@
       <c r="S924" s="3"/>
       <c r="T924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -21619,7 +21754,7 @@
       <c r="S925" s="3"/>
       <c r="T925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -21641,7 +21776,7 @@
       <c r="S926" s="3"/>
       <c r="T926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -21663,7 +21798,7 @@
       <c r="S927" s="3"/>
       <c r="T927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -21685,7 +21820,7 @@
       <c r="S928" s="3"/>
       <c r="T928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -21707,7 +21842,7 @@
       <c r="S929" s="3"/>
       <c r="T929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -21729,7 +21864,7 @@
       <c r="S930" s="3"/>
       <c r="T930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -21751,7 +21886,7 @@
       <c r="S931" s="3"/>
       <c r="T931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -21773,7 +21908,7 @@
       <c r="S932" s="3"/>
       <c r="T932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -21795,7 +21930,7 @@
       <c r="S933" s="3"/>
       <c r="T933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -21817,7 +21952,7 @@
       <c r="S934" s="3"/>
       <c r="T934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -21839,7 +21974,7 @@
       <c r="S935" s="3"/>
       <c r="T935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -21861,7 +21996,7 @@
       <c r="S936" s="3"/>
       <c r="T936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -21883,7 +22018,7 @@
       <c r="S937" s="3"/>
       <c r="T937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -21905,7 +22040,7 @@
       <c r="S938" s="3"/>
       <c r="T938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -21927,7 +22062,7 @@
       <c r="S939" s="3"/>
       <c r="T939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -21949,7 +22084,7 @@
       <c r="S940" s="3"/>
       <c r="T940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -21971,7 +22106,7 @@
       <c r="S941" s="3"/>
       <c r="T941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -21993,7 +22128,7 @@
       <c r="S942" s="3"/>
       <c r="T942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -22015,7 +22150,7 @@
       <c r="S943" s="3"/>
       <c r="T943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -22037,7 +22172,7 @@
       <c r="S944" s="3"/>
       <c r="T944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -22059,7 +22194,7 @@
       <c r="S945" s="3"/>
       <c r="T945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -22081,7 +22216,7 @@
       <c r="S946" s="3"/>
       <c r="T946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -22103,7 +22238,7 @@
       <c r="S947" s="3"/>
       <c r="T947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -22125,7 +22260,7 @@
       <c r="S948" s="3"/>
       <c r="T948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -22147,7 +22282,7 @@
       <c r="S949" s="3"/>
       <c r="T949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -22169,7 +22304,7 @@
       <c r="S950" s="3"/>
       <c r="T950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -22191,7 +22326,7 @@
       <c r="S951" s="3"/>
       <c r="T951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -22213,7 +22348,7 @@
       <c r="S952" s="3"/>
       <c r="T952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -22235,7 +22370,7 @@
       <c r="S953" s="3"/>
       <c r="T953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -22257,7 +22392,7 @@
       <c r="S954" s="3"/>
       <c r="T954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -22279,7 +22414,7 @@
       <c r="S955" s="3"/>
       <c r="T955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -22301,7 +22436,7 @@
       <c r="S956" s="3"/>
       <c r="T956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -22323,7 +22458,7 @@
       <c r="S957" s="3"/>
       <c r="T957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -22345,7 +22480,7 @@
       <c r="S958" s="3"/>
       <c r="T958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -22367,7 +22502,7 @@
       <c r="S959" s="3"/>
       <c r="T959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -22389,7 +22524,7 @@
       <c r="S960" s="3"/>
       <c r="T960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -22411,7 +22546,7 @@
       <c r="S961" s="3"/>
       <c r="T961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -22433,7 +22568,7 @@
       <c r="S962" s="3"/>
       <c r="T962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -22455,7 +22590,7 @@
       <c r="S963" s="3"/>
       <c r="T963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -22477,7 +22612,7 @@
       <c r="S964" s="3"/>
       <c r="T964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -22499,7 +22634,7 @@
       <c r="S965" s="3"/>
       <c r="T965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -22521,7 +22656,7 @@
       <c r="S966" s="3"/>
       <c r="T966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -22543,7 +22678,7 @@
       <c r="S967" s="3"/>
       <c r="T967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -22565,7 +22700,7 @@
       <c r="S968" s="3"/>
       <c r="T968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -22587,7 +22722,7 @@
       <c r="S969" s="3"/>
       <c r="T969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -22609,7 +22744,7 @@
       <c r="S970" s="3"/>
       <c r="T970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -22631,7 +22766,7 @@
       <c r="S971" s="3"/>
       <c r="T971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -22653,7 +22788,7 @@
       <c r="S972" s="3"/>
       <c r="T972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -22675,7 +22810,7 @@
       <c r="S973" s="3"/>
       <c r="T973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -22697,7 +22832,7 @@
       <c r="S974" s="3"/>
       <c r="T974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -22719,7 +22854,7 @@
       <c r="S975" s="3"/>
       <c r="T975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -22741,7 +22876,7 @@
       <c r="S976" s="3"/>
       <c r="T976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -22763,7 +22898,7 @@
       <c r="S977" s="3"/>
       <c r="T977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -22785,7 +22920,7 @@
       <c r="S978" s="3"/>
       <c r="T978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -22807,7 +22942,7 @@
       <c r="S979" s="3"/>
       <c r="T979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -22829,7 +22964,7 @@
       <c r="S980" s="3"/>
       <c r="T980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -22851,7 +22986,7 @@
       <c r="S981" s="3"/>
       <c r="T981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -22873,7 +23008,7 @@
       <c r="S982" s="3"/>
       <c r="T982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -22895,7 +23030,7 @@
       <c r="S983" s="3"/>
       <c r="T983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -22917,7 +23052,7 @@
       <c r="S984" s="3"/>
       <c r="T984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -22939,7 +23074,7 @@
       <c r="S985" s="3"/>
       <c r="T985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -22961,7 +23096,7 @@
       <c r="S986" s="3"/>
       <c r="T986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -22983,7 +23118,7 @@
       <c r="S987" s="3"/>
       <c r="T987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -23005,7 +23140,7 @@
       <c r="S988" s="3"/>
       <c r="T988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -23027,7 +23162,7 @@
       <c r="S989" s="3"/>
       <c r="T989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -23049,7 +23184,7 @@
       <c r="S990" s="3"/>
       <c r="T990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -23071,7 +23206,7 @@
       <c r="S991" s="3"/>
       <c r="T991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -23093,7 +23228,7 @@
       <c r="S992" s="3"/>
       <c r="T992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -23115,7 +23250,7 @@
       <c r="S993" s="3"/>
       <c r="T993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -23137,7 +23272,7 @@
       <c r="S994" s="3"/>
       <c r="T994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -23159,7 +23294,7 @@
       <c r="S995" s="3"/>
       <c r="T995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -23181,7 +23316,7 @@
       <c r="S996" s="3"/>
       <c r="T996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -23203,7 +23338,7 @@
       <c r="S997" s="3"/>
       <c r="T997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -23225,7 +23360,7 @@
       <c r="S998" s="3"/>
       <c r="T998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -23247,7 +23382,7 @@
       <c r="S999" s="3"/>
       <c r="T999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1000" s="3"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
@@ -23270,6 +23405,6 @@
       <c r="T1000" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>